--- a/artfynd/A 32655-2024 artfynd.xlsx
+++ b/artfynd/A 32655-2024 artfynd.xlsx
@@ -1981,7 +1981,7 @@
         <v>119257071</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>119266934</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>119266936</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>119266933</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>119266935</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>119266932</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>119266937</v>
       </c>
       <c r="B116" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 32655-2024 artfynd.xlsx
+++ b/artfynd/A 32655-2024 artfynd.xlsx
@@ -1981,7 +1981,7 @@
         <v>119257071</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>119266934</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>119266936</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>119266933</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>119266935</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>119266932</v>
       </c>
       <c r="B92" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>119266937</v>
       </c>
       <c r="B116" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 32655-2024 artfynd.xlsx
+++ b/artfynd/A 32655-2024 artfynd.xlsx
@@ -1981,7 +1981,7 @@
         <v>119257071</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>119266934</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>119266936</v>
       </c>
       <c r="B57" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>119266933</v>
       </c>
       <c r="B67" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>119266935</v>
       </c>
       <c r="B71" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>119266932</v>
       </c>
       <c r="B92" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>119266937</v>
       </c>
       <c r="B116" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 32655-2024 artfynd.xlsx
+++ b/artfynd/A 32655-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AZ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260241</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260371</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260637</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263605</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263823</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119259687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264252</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264303</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266992</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264309</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266928</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266929</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266930</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266931</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261685</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264173</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260513</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2634,6 +2729,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260709</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2739,6 +2839,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263856</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263975</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266991</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3042,6 +3157,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264376</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3149,6 +3269,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260013</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3256,6 +3381,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119256993</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3363,6 +3493,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257779</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3470,6 +3605,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119259572</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3577,6 +3717,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119259605</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3684,6 +3829,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260894</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3791,6 +3941,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261595</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3898,6 +4053,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261602</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4005,6 +4165,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4116,6 +4281,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263268</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4227,6 +4397,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263319</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4338,6 +4513,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263412</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4449,6 +4629,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263427</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4550,6 +4735,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263706</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4655,6 +4845,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263919</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4760,6 +4955,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264136</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4865,6 +5065,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264170</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4966,6 +5171,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264325</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5067,6 +5277,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264340</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5174,6 +5389,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257725</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5281,6 +5501,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257843</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5388,6 +5613,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261806</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5499,6 +5729,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263301</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5610,6 +5845,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263390</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5721,6 +5961,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263402</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5832,6 +6077,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263431</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5943,6 +6193,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263438</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6044,6 +6299,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264194</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6145,6 +6405,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264245</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6246,6 +6511,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264256</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6347,6 +6617,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264263</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6452,6 +6727,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264284</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6553,6 +6833,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264383</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6650,6 +6935,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266940</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6747,6 +7037,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266941</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6844,6 +7139,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266942</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6941,6 +7241,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266943</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7038,6 +7343,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266944</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7135,6 +7445,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266945</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7232,6 +7547,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266946</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7329,6 +7649,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266947</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7426,6 +7751,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266948</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7523,6 +7853,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266949</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7620,6 +7955,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266950</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7717,6 +8057,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266952</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7818,6 +8163,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264287</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7925,6 +8275,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257411</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8032,6 +8387,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257740</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8133,6 +8493,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264213</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8234,6 +8599,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264268</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8351,6 +8721,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257071</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8453,6 +8828,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266932</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8555,6 +8935,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266933</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8657,6 +9042,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266934</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8759,6 +9149,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266935</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8861,6 +9256,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266936</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8963,6 +9363,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266937</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9064,6 +9469,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264368</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9171,6 +9581,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258770</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9290,6 +9705,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263254</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9395,6 +9815,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264317</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9502,6 +9927,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263966</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9618,6 +10048,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257355</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9734,6 +10169,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119257674</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9850,6 +10290,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258085</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9966,6 +10411,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258766</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10087,6 +10537,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119259937</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10203,6 +10658,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260143</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10319,6 +10779,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260256</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10435,6 +10900,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260288</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10542,6 +11012,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260352</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10658,6 +11133,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260724</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10774,6 +11254,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261100</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10881,6 +11366,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261671</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10997,6 +11487,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261741</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11117,6 +11612,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263176</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11237,6 +11737,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263222</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11353,6 +11858,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119263419</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11463,6 +11973,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264222</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11573,6 +12088,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264232</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11683,6 +12203,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264289</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11793,6 +12318,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264361</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11895,6 +12425,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264397</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11997,6 +12532,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119264405</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12099,6 +12639,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266060</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12196,6 +12741,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266958</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12293,6 +12843,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266959</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12390,6 +12945,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266960</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12487,6 +13047,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266961</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12584,6 +13149,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266962</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12681,6 +13251,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266963</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12778,6 +13353,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266964</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12875,6 +13455,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266965</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12972,6 +13557,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266966</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13069,6 +13659,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266967</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13166,6 +13761,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266968</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13263,6 +13863,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266969</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13360,6 +13965,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266970</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13457,6 +14067,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266971</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13554,6 +14169,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266972</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13651,6 +14271,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266973</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13748,6 +14373,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266974</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13845,6 +14475,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266975</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13942,6 +14577,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266976</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14039,6 +14679,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266977</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14136,6 +14781,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266978</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14233,6 +14883,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266979</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14330,6 +14985,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266980</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14427,6 +15087,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266981</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14524,6 +15189,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266938</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14621,8 +15291,149 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119266939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>